--- a/docs/downloads/经营分_河南省区__郑州中片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__郑州中片区_2026-10-18.xlsx
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I2" t="n">
-        <v>-30</v>
+        <v>-35</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
         <v>30</v>
@@ -1043,17 +1043,17 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7393183521952499738</t>
+          <t>7359054569706129471</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>潮漫酒店（郑州高铁东站东广场店）</t>
+          <t>白玉兰商务酒店（郑州高铁东站东广场店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>潮漫酒店(郑州高铁东站东广场店)</t>
+          <t>白玉兰酒店(郑州高铁东站东广场店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1131,29 +1131,29 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7359054569706129471</t>
+          <t>7278635278892271657</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（郑州高铁东站东广场店）</t>
+          <t>IU酒店（郑州高铁站店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>白玉兰酒店(郑州高铁东站东广场店)</t>
+          <t>iu酒店(郑州高铁站店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1219,29 +1219,29 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7278635278892271657</t>
+          <t>7393183521952499738</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IU酒店（郑州高铁站店）</t>
+          <t>潮漫酒店（郑州高铁东站东广场店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>iu酒店(郑州高铁站店)</t>
+          <t>潮漫酒店(郑州高铁东站东广场店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>85</v>
       </c>
       <c r="I8" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1307,26 +1307,26 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7442600835101493248</t>
+          <t>6601136656672098318</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>锦江之星（ 郑州中原博览中心凤凰台南地铁站店）</t>
+          <t>希岸酒店（郑州国基路海洋馆店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>锦江之星5.0(凤凰茶城凤凰台南地铁站)</t>
+          <t>希岸酒店(郑州国基路店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601136656672098318</t>
+          <t>6763560298612918276</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>希岸酒店（郑州国基路海洋馆店）</t>
+          <t>喆啡酒店（郑州北龙湖湿地公园店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>希岸酒店(郑州国基路店)</t>
+          <t>喆啡酒店(郑州北龙湖湿地公园店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
@@ -1483,22 +1483,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6763560298612918276</t>
+          <t>6638774274511407108</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>喆啡酒店（郑州北龙湖湿地公园店）</t>
+          <t>维也纳酒店（郑州航海广场地铁站店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>喆啡酒店(郑州北龙湖湿地公园店)</t>
+          <t>维也纳酒店(郑州航海广场地铁站店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6638774274511407108</t>
+          <t>7442600835101493248</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>维也纳酒店（郑州航海广场地铁站店）</t>
+          <t>锦江之星（ 郑州中原博览中心凤凰台南地铁站店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳酒店(郑州航海广场地铁站店)</t>
+          <t>锦江之星5.0(凤凰茶城凤凰台南地铁站)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
@@ -1619,7 +1619,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -2561,7 +2561,7 @@
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2979,26 +2979,26 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7377218965892532261</t>
+          <t>6601137316180264974</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>维也纳酒店（郑州火车站西广场店）</t>
+          <t>7天酒店(郑州二七广场东大街地铁站店)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>维也纳酒店(郑州火车站西广场店)</t>
+          <t>7天酒店(郑州二七广场东大街地铁站店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3067,33 +3067,33 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6601137316180264974</t>
+          <t>6676596821961263107</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7天酒店(郑州二七广场东大街地铁站店)</t>
+          <t>希岸酒店（郑州海亮时代广场刘庄地铁站店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7天酒店(郑州二七广场东大街地铁站店)</t>
+          <t>希岸酒店(郑州海亮时代广场刘庄地铁站店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>110</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3103,7 +3103,7 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
@@ -3115,7 +3115,7 @@
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3155,17 +3155,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7404682705012525119</t>
+          <t>7555323906568800265</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（3.0版郑州亳都新象文庙地铁站店）</t>
+          <t>维也纳酒店(郑州高铁东站东广场圃田西地铁站店)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(郑州亳都新象文庙地铁站店)</t>
+          <t>维也纳酒店(郑州高铁东站东广场圃田西地铁站店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3177,7 +3177,7 @@
         <v>110</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -3243,22 +3243,22 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6676596821961263107</t>
+          <t>7377218965892532261</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>希岸酒店（郑州海亮时代广场刘庄地铁站店）</t>
+          <t>维也纳酒店（郑州火车站西广场店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>希岸酒店(郑州海亮时代广场刘庄地铁站店)</t>
+          <t>维也纳酒店(郑州火车站西广场店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3279,7 +3279,7 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>30</v>
@@ -3291,7 +3291,7 @@
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>7555323906568800265</t>
+          <t>7278635151330904083</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>维也纳酒店(郑州高铁东站东广场圃田西地铁站店)</t>
+          <t>锦江之星（郑州海洋馆正弘城文化路店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>维也纳酒店(郑州高铁东站东广场圃田西地铁站店)</t>
+          <t>锦江之星(正弘城文化路店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3353,11 +3353,11 @@
         <v>110</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3373,13 +3373,13 @@
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R32" t="n">
         <v>30</v>
@@ -3419,17 +3419,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7278635151330904083</t>
+          <t>6846339878439929863</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>锦江之星（郑州海洋馆正弘城文化路店）</t>
+          <t>麗枫酒店（郑州航海东路经开中心广场地铁站店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>锦江之星(正弘城文化路店)</t>
+          <t>麗枫酒店(郑州航海东路经开中心广场地铁站店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3441,11 +3441,11 @@
         <v>110</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -3461,13 +3461,13 @@
         <v>30</v>
       </c>
       <c r="O33" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P33" t="n">
         <v>30</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
         <v>30</v>
@@ -3507,26 +3507,26 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>6846339878439929863</t>
+          <t>7548407514338248723</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>麗枫酒店（郑州航海东路经开中心广场地铁站店）</t>
+          <t>7天酒店智选版（郑州东站西周地铁站店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>麗枫酒店(郑州航海东路经开中心广场地铁站店)</t>
+          <t>7天酒店智选版(郑州东站西周地铁站店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         <v>30</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R34" t="n">
         <v>30</v>
@@ -3595,33 +3595,33 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>7548407514338248723</t>
+          <t>6601141203914196995</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7天酒店智选版（郑州东站西周地铁站店）</t>
+          <t>7天酒店（郑州二七广场人民路地铁站店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>7天酒店智选版(郑州东站西周地铁站店)</t>
+          <t>7天酒店(郑州二七广场人民路地铁站店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>115</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3631,7 +3631,7 @@
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N35" t="n">
         <v>30</v>
@@ -3643,7 +3643,7 @@
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
@@ -3683,33 +3683,33 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>6601141203914196995</t>
+          <t>7404682705012525119</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7天酒店（郑州二七广场人民路地铁站店）</t>
+          <t>凯里亚德酒店（3.0版郑州亳都新象文庙地铁站店）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7天酒店(郑州二七广场人民路地铁站店)</t>
+          <t>凯里亚德酒店(郑州亳都新象文庙地铁站店)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>115</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -3719,19 +3719,19 @@
         <v>10</v>
       </c>
       <c r="M36" t="n">
+        <v>30</v>
+      </c>
+      <c r="N36" t="n">
+        <v>30</v>
+      </c>
+      <c r="O36" t="n">
+        <v>30</v>
+      </c>
+      <c r="P36" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q36" t="n">
         <v>25</v>
-      </c>
-      <c r="N36" t="n">
-        <v>30</v>
-      </c>
-      <c r="O36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P36" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>30</v>
       </c>
       <c r="R36" t="n">
         <v>30</v>
@@ -3969,7 +3969,7 @@
         <v>115</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
